--- a/resources/Part_3_Statistics/S18_L105/3.9.Population-variance-known-z-score-exercise.xlsx
+++ b/resources/Part_3_Statistics/S18_L105/3.9.Population-variance-known-z-score-exercise.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18229"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iliya\Desktop\Statistics Course\Filming\Final excel\Section 3 - Inferential\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\GitRepos\StatisticsBAandDS\DataScienceBootcamp\resources\Part_3_Statistics\S18_L105\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9084"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="6" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Data scientist salary</t>
   </si>
@@ -57,6 +57,30 @@
   </si>
   <si>
     <t>You are given the same dataset from the lesson. The population standard deviation is known to be $ 15,000.</t>
+  </si>
+  <si>
+    <t>mean =</t>
+  </si>
+  <si>
+    <t>90% interval -&gt; alpha=10% = 0.1</t>
+  </si>
+  <si>
+    <t>Find the Z-score for 0.05</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>search for 0.95 in the table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
   </si>
 </sst>
 </file>
@@ -64,8 +88,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -153,9 +177,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -164,10 +188,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -178,15 +202,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -499,33 +527,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N40"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="4" style="1" customWidth="1"/>
-    <col min="9" max="10" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
@@ -533,7 +561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
@@ -541,7 +569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
@@ -549,7 +577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
@@ -557,17 +585,40 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1">
+        <f>SUM(B11:B40)/COUNT(B11:B40)</f>
+        <v>100200.36666666667</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B11" s="6">
         <v>117313</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="14">
+        <f>15000/SQRT(COUNT(B11:B40))</f>
+        <v>2738.6127875258308</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
         <v>104002</v>
       </c>
@@ -579,7 +630,9 @@
       <c r="H12" s="9"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B13" s="6">
@@ -595,22 +648,32 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>101936</v>
       </c>
       <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
+      <c r="D14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="12">
+        <f>E10-(1.65*15000/SQRT(COUNT(B11:B40)))</f>
+        <v>95681.65556724905</v>
+      </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="15">
+        <f>E10+(1.65*15000/SQRT(COUNT(B11:B40)))</f>
+        <v>104719.07776608429</v>
+      </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
       <c r="K14" s="8"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B15" s="6">
         <v>84560</v>
       </c>
@@ -624,7 +687,7 @@
       <c r="J15" s="12"/>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B16" s="6">
         <v>113136</v>
       </c>
@@ -653,7 +716,7 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="6">
         <v>100536</v>
       </c>
@@ -667,7 +730,7 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="6">
         <v>105052</v>
       </c>
